--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,14 +851,14 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -873,16 +873,16 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N14" s="15">
         <v>-87.5</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
@@ -901,23 +901,23 @@
       <c r="E15" s="15">
         <v>-100</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>2</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>-50</v>
@@ -926,258 +926,258 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.142857142857</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>-18.181818181818</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K16" s="15">
-        <v>-27.272727272727</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.454545454545</v>
+        <v>-52.727272727272</v>
       </c>
       <c r="M16" s="15">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.397849462365</v>
+        <v>-92.215568862275</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.857142857142</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G17" s="14">
         <v>50</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I17" s="14">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="J17" s="14">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.333333333333</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.455696202531</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>69.230769230769</v>
+        <v>81.395348837209</v>
       </c>
       <c r="N17" s="15">
-        <v>-38.888888888888</v>
+        <v>-41.791044776119</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
         <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-71.428571428571</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I18" s="14">
         <v>14</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L18" s="15">
-        <v>-44</v>
+        <v>-54.838709677419</v>
       </c>
       <c r="M18" s="15">
-        <v>-69.565217391304</v>
+        <v>-72</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.142259414225</v>
+        <v>-94.852941176470</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
+        <v>8</v>
+      </c>
+      <c r="D19" s="14">
         <v>10</v>
       </c>
-      <c r="D19" s="14">
-        <v>13</v>
-      </c>
       <c r="E19" s="15">
-        <v>-23.076923076923</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>5.714285714285</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I19" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J19" s="14">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="K19" s="15">
-        <v>8.695652173913</v>
+        <v>5.357142857142</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.354838709677</v>
+        <v>-23.376623376623</v>
       </c>
       <c r="M19" s="15">
-        <v>-21.875</v>
+        <v>-22.368421052631</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.5</v>
+        <v>-35.164835164835</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
         <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>250</v>
+        <v>-30</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>128.571428571429</v>
+        <v>20</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K20" s="15">
-        <v>53.846153846153</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L20" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>-45.945945945945</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.248062015503</v>
+        <v>-91</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
         <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E21" s="18">
-        <v>-25.641025641025</v>
+        <v>-40.816326530612</v>
       </c>
       <c r="F21" s="17">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G21" s="17">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.617647058823</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I21" s="17">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="J21" s="17">
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.290155440414</v>
+        <v>-14.462809917355</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.043478260869</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.630252100840</v>
+        <v>-22.471910112359</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.920326864147</v>
+        <v>-81.968641114982</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
@@ -1204,7 +1204,7 @@
         <v>20</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L22" s="15">
         <v>-100</v>
@@ -1213,7 +1213,7 @@
         <v>-100</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>36.842105263157</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G24" s="14">
         <v>84</v>
       </c>
       <c r="H24" s="15">
-        <v>15.476190476190</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I24" s="14">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="J24" s="14">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="K24" s="15">
-        <v>24.324324324324</v>
+        <v>26.923076923076</v>
       </c>
       <c r="L24" s="15">
-        <v>6.976744186046</v>
+        <v>10.738255033557</v>
       </c>
       <c r="M24" s="15">
-        <v>27.777777777777</v>
+        <v>35.245901639344</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>266.666666666667</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
         <v>25</v>
       </c>
       <c r="G25" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>108.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J25" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K25" s="15">
-        <v>47.619047619047</v>
+        <v>36</v>
       </c>
       <c r="L25" s="15">
-        <v>40.909090909090</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-17.647058823529</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G26" s="14">
         <v>54</v>
       </c>
       <c r="H26" s="15">
-        <v>14.814814814814</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I26" s="14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J26" s="14">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K26" s="15">
-        <v>6.666666666666</v>
+        <v>3.448275862068</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.976744186046</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.191919191919</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1394,31 +1394,31 @@
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L27" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1429,119 +1429,119 @@
         <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>-75</v>
+      </c>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1635,13 +1635,13 @@
         <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>91</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>2158</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>975</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>2607</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>699</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>2418</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>9002</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,49 +854,49 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>4</v>
       </c>
       <c r="K14" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L14" s="15">
+        <v>100</v>
+      </c>
+      <c r="M14" s="15">
+        <v>-60</v>
+      </c>
+      <c r="N14" s="15">
         <v>-75</v>
-      </c>
-      <c r="L14" s="15">
-        <v>0</v>
-      </c>
-      <c r="M14" s="15">
-        <v>-80</v>
-      </c>
-      <c r="N14" s="15">
-        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -914,270 +914,270 @@
         <v>2</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M15" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-81.818181818181</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
         <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>-51.612903225806</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="I16" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J16" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>-40.909090909090</v>
+        <v>-38.775510204081</v>
       </c>
       <c r="L16" s="15">
-        <v>-52.727272727272</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.215568862275</v>
+        <v>-91.957104557640</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>18</v>
+      </c>
+      <c r="D17" s="14">
         <v>12</v>
       </c>
-      <c r="D17" s="14">
-        <v>15</v>
-      </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G17" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H17" s="15">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="J17" s="14">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.344827586206</v>
+        <v>-4.040404040404</v>
       </c>
       <c r="L17" s="15">
-        <v>-13.333333333333</v>
+        <v>-4.040404040404</v>
       </c>
       <c r="M17" s="15">
-        <v>81.395348837209</v>
+        <v>97.916666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-41.791044776119</v>
+        <v>-38.311688311688</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>4</v>
+      </c>
+      <c r="G18" s="14">
+        <v>8</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I18" s="14">
+        <v>15</v>
+      </c>
+      <c r="J18" s="14">
         <v>24</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="14">
-        <v>3</v>
-      </c>
-      <c r="G18" s="14">
-        <v>11</v>
-      </c>
-      <c r="H18" s="15">
+      <c r="K18" s="15">
+        <v>-37.5</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-59.459459459459</v>
+      </c>
+      <c r="M18" s="15">
         <v>-72.727272727272</v>
       </c>
-      <c r="I18" s="14">
-        <v>14</v>
-      </c>
-      <c r="J18" s="14">
-        <v>22</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-36.363636363636</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-54.838709677419</v>
-      </c>
-      <c r="M18" s="15">
-        <v>-72</v>
-      </c>
       <c r="N18" s="15">
-        <v>-94.852941176470</v>
+        <v>-94.966442953020</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.384615384615</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="I19" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J19" s="14">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="K19" s="15">
-        <v>5.357142857142</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.376623376623</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="M19" s="15">
-        <v>-22.368421052631</v>
+        <v>-24.705882352941</v>
       </c>
       <c r="N19" s="15">
-        <v>-35.164835164835</v>
+        <v>-37.254901960784</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F20" s="14">
+        <v>17</v>
+      </c>
+      <c r="G20" s="14">
+        <v>18</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-5.555555555555</v>
+      </c>
+      <c r="I20" s="14">
+        <v>28</v>
+      </c>
+      <c r="J20" s="14">
         <v>26</v>
       </c>
-      <c r="C20" s="14">
-        <v>7</v>
-      </c>
-      <c r="D20" s="14">
-        <v>10</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-30</v>
-      </c>
-      <c r="F20" s="14">
-        <v>18</v>
-      </c>
-      <c r="G20" s="14">
-        <v>15</v>
-      </c>
-      <c r="H20" s="15">
-        <v>20</v>
-      </c>
-      <c r="I20" s="14">
-        <v>27</v>
-      </c>
-      <c r="J20" s="14">
-        <v>23</v>
-      </c>
       <c r="K20" s="15">
-        <v>17.391304347826</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L20" s="15">
-        <v>28.571428571428</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-28.947368421052</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-91</v>
+        <v>-91.860465116279</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>-40.816326530612</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F21" s="17">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.727272727272</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="I21" s="17">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="J21" s="17">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.462809917355</v>
+        <v>-15.714285714285</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.806451612903</v>
+        <v>-22.875816993464</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.471910112359</v>
+        <v>-22.875816993464</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.968641114982</v>
+        <v>-81.691233514352</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
@@ -1204,7 +1204,7 @@
         <v>20</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L22" s="15">
         <v>-100</v>
@@ -1213,7 +1213,7 @@
         <v>-100</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>36.842105263157</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G24" s="14">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H24" s="15">
-        <v>19.047619047619</v>
+        <v>9.411764705882</v>
       </c>
       <c r="I24" s="14">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="J24" s="14">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="K24" s="15">
-        <v>26.923076923076</v>
+        <v>22.727272727272</v>
       </c>
       <c r="L24" s="15">
-        <v>10.738255033557</v>
+        <v>15.950920245398</v>
       </c>
       <c r="M24" s="15">
-        <v>35.245901639344</v>
+        <v>34.042553191489</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1305,38 +1305,38 @@
       <c r="C25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="14">
-        <v>4</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-25</v>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H25" s="15">
         <v>66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J25" s="14">
         <v>25</v>
       </c>
       <c r="K25" s="15">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L25" s="15">
-        <v>30.769230769230</v>
+        <v>32.142857142857</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F26" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G26" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>18.518518518518</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I26" s="14">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J26" s="14">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="K26" s="15">
-        <v>3.448275862068</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.285714285714</v>
+        <v>-14.049586776859</v>
       </c>
       <c r="M26" s="15">
-        <v>-23.076923076923</v>
+        <v>-22.388059701492</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1388,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
@@ -1406,19 +1406,19 @@
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1428,38 +1428,38 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1476,31 +1476,31 @@
         <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-83.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.117647058823</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" s="15">
-        <v>-83.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.117647058823</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1635,13 +1635,13 @@
         <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>91</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>2158</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>975</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>2607</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>699</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>2418</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>9002</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -864,10 +864,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-80</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>-48.387096774193</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J16" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K16" s="15">
-        <v>-38.775510204081</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="L16" s="15">
-        <v>-48.275862068965</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.846153846153</v>
+        <v>-52.777777777777</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.957104557640</v>
+        <v>-92.147806004618</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
+        <v>18.181818181818</v>
+      </c>
+      <c r="F17" s="14">
         <v>50</v>
       </c>
-      <c r="F17" s="14">
-        <v>55</v>
-      </c>
       <c r="G17" s="14">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I17" s="14">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="J17" s="14">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.040404040404</v>
+        <v>-1.818181818181</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.040404040404</v>
+        <v>-4.424778761061</v>
       </c>
       <c r="M17" s="15">
-        <v>97.916666666666</v>
+        <v>86.206896551724</v>
       </c>
       <c r="N17" s="15">
-        <v>-38.311688311688</v>
+        <v>-34.939759036144</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.5</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="L18" s="15">
-        <v>-59.459459459459</v>
+        <v>-57.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-72.727272727272</v>
+        <v>-73.4375</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.966442953020</v>
+        <v>-94.817073170731</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-71.428571428571</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H19" s="15">
-        <v>-32.608695652173</v>
+        <v>-35.185185185185</v>
       </c>
       <c r="I19" s="14">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="J19" s="14">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.571428571428</v>
+        <v>-12.643678160919</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.951219512195</v>
+        <v>-22.448979591836</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.705882352941</v>
+        <v>-23.232323232323</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.254901960784</v>
+        <v>-35.042735042735</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
         <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-5.555555555555</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
+        <v>30</v>
+      </c>
+      <c r="J20" s="14">
         <v>28</v>
       </c>
-      <c r="J20" s="14">
-        <v>26</v>
-      </c>
       <c r="K20" s="15">
-        <v>7.692307692307</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L20" s="15">
-        <v>16.666666666666</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M20" s="15">
-        <v>-37.777777777777</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.860465116279</v>
+        <v>-92.063492063492</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.315789473684</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G21" s="17">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.242424242424</v>
+        <v>-28.402366863905</v>
       </c>
       <c r="I21" s="17">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="J21" s="17">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.714285714285</v>
+        <v>-16.408668730650</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.875816993464</v>
+        <v>-21.511627906976</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.875816993464</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.691233514352</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,32 +1223,32 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-100</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>21</v>
+      <c r="J23" s="14">
+        <v>3</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-100</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>15.789473684210</v>
       </c>
       <c r="F24" s="14">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G24" s="14">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" s="15">
-        <v>9.411764705882</v>
+        <v>11.627906976744</v>
       </c>
       <c r="I24" s="14">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="J24" s="14">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="K24" s="15">
-        <v>22.727272727272</v>
+        <v>21.387283236994</v>
       </c>
       <c r="L24" s="15">
-        <v>15.950920245398</v>
+        <v>5</v>
       </c>
       <c r="M24" s="15">
-        <v>34.042553191489</v>
+        <v>30.434782608695</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D25" s="14">
+        <v>5</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
         <v>12</v>
       </c>
       <c r="H25" s="15">
-        <v>66.666666666666</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J25" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K25" s="15">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="L25" s="15">
-        <v>32.142857142857</v>
+        <v>25.806451612903</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>55.555555555555</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F26" s="14">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H26" s="15">
-        <v>18.181818181818</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="I26" s="14">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="J26" s="14">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="K26" s="15">
-        <v>8.333333333333</v>
+        <v>0.869565217391</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.049586776859</v>
+        <v>-18.881118881118</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.388059701492</v>
+        <v>-21.088435374149</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1403,16 +1403,16 @@
         <v>-80</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
+        <v>-6.666666666666</v>
+      </c>
+      <c r="L28" s="15">
         <v>16.666666666666</v>
-      </c>
-      <c r="L28" s="15">
-        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,23 +1466,23 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1497,33 +1497,33 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-71.428571428571</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1538,10 +1538,10 @@
         <v>100</v>
       </c>
       <c r="M30" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.476190476190</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="15">
         <v>-100</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -861,13 +861,13 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -902,31 +902,31 @@
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-70</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -946,28 +946,28 @@
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="I16" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.615384615384</v>
+        <v>-32.727272727272</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.333333333333</v>
+        <v>-47.142857142857</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.777777777777</v>
+        <v>-54.320987654321</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.147806004618</v>
+        <v>-92.433537832310</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,51 +978,51 @@
         <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G17" s="14">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.846153846153</v>
+        <v>7.843137254901</v>
       </c>
       <c r="I17" s="14">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J17" s="14">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.818181818181</v>
+        <v>-1.626016260162</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.424778761061</v>
+        <v>-5.46875</v>
       </c>
       <c r="M17" s="15">
-        <v>86.206896551724</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.939759036144</v>
+        <v>-34.239130434782</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>9</v>
-      </c>
       <c r="E18" s="15">
-        <v>-77.777777777777</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -1037,19 +1037,19 @@
         <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-48.484848484848</v>
+        <v>-51.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-57.5</v>
+        <v>-59.523809523809</v>
       </c>
       <c r="M18" s="15">
-        <v>-73.4375</v>
+        <v>-76.712328767123</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.817073170731</v>
+        <v>-95.490716180371</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-29.411764705882</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H19" s="15">
-        <v>-35.185185185185</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J19" s="14">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.643678160919</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.448979591836</v>
+        <v>-22.321428571428</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.232323232323</v>
+        <v>-16.346153846153</v>
       </c>
       <c r="N19" s="15">
-        <v>-35.042735042735</v>
+        <v>-32.558139534883</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="15">
-        <v>7.142857142857</v>
+        <v>13.793103448275</v>
       </c>
       <c r="L20" s="15">
-        <v>15.384615384615</v>
+        <v>13.793103448275</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-43.103448275862</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.063492063492</v>
+        <v>-92.216981132075</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.930232558139</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G21" s="17">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.402366863905</v>
+        <v>-24.848484848484</v>
       </c>
       <c r="I21" s="17">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="J21" s="17">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.408668730650</v>
+        <v>-15.921787709497</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.511627906976</v>
+        <v>-22.422680412371</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.076923076923</v>
+        <v>-23.017902813299</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.25</v>
+        <v>-81.476923076923</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,11 +1223,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>15.789473684210</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F24" s="14">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H24" s="15">
-        <v>11.627906976744</v>
+        <v>16</v>
       </c>
       <c r="I24" s="14">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="J24" s="14">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="K24" s="15">
-        <v>21.387283236994</v>
+        <v>21.505376344086</v>
       </c>
       <c r="L24" s="15">
-        <v>5</v>
+        <v>3.196347031963</v>
       </c>
       <c r="M24" s="15">
-        <v>30.434782608695</v>
+        <v>25.555555555555</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="14">
-        <v>5</v>
-      </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>58.333333333333</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I25" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J25" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K25" s="15">
-        <v>30</v>
+        <v>40.625</v>
       </c>
       <c r="L25" s="15">
-        <v>25.806451612903</v>
+        <v>40.625</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>-31.578947368421</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F26" s="14">
         <v>50</v>
       </c>
       <c r="G26" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.280701754386</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I26" s="14">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="J26" s="14">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="K26" s="15">
-        <v>0.869565217391</v>
+        <v>-5.109489051094</v>
       </c>
       <c r="L26" s="15">
-        <v>-18.881118881118</v>
+        <v>-20.731707317073</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.088435374149</v>
+        <v>-18.75</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L27" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-6.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-92</v>
+        <v>-92.592592592592</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,17 +1625,17 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="D14" s="14">
         <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L14" s="15">
         <v>100</v>
@@ -890,212 +890,212 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-60</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N15" s="15">
-        <v>-71.428571428571</v>
+        <v>-61.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
         <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-40.909090909090</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>-32.727272727272</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L16" s="15">
-        <v>-47.142857142857</v>
+        <v>-43.243243243243</v>
       </c>
       <c r="M16" s="15">
-        <v>-54.320987654321</v>
+        <v>-52.808988764044</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.433537832310</v>
+        <v>-92.193308550185</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
         <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F17" s="14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G17" s="14">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H17" s="15">
-        <v>7.843137254901</v>
+        <v>2.040816326530</v>
       </c>
       <c r="I17" s="14">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J17" s="14">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.626016260162</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.46875</v>
+        <v>-12.925170068027</v>
       </c>
       <c r="M17" s="15">
-        <v>83.333333333333</v>
+        <v>75.342465753424</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.239130434782</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
         <v>14</v>
       </c>
       <c r="H18" s="15">
+        <v>-71.428571428571</v>
+      </c>
+      <c r="I18" s="14">
+        <v>18</v>
+      </c>
+      <c r="J18" s="14">
+        <v>36</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-60.869565217391</v>
+      </c>
+      <c r="M18" s="15">
         <v>-78.571428571428</v>
       </c>
-      <c r="I18" s="14">
-        <v>17</v>
-      </c>
-      <c r="J18" s="14">
-        <v>35</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-51.428571428571</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-59.523809523809</v>
-      </c>
-      <c r="M18" s="15">
-        <v>-76.712328767123</v>
-      </c>
       <c r="N18" s="15">
-        <v>-95.490716180371</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
+        <v>6</v>
+      </c>
+      <c r="D19" s="14">
         <v>12</v>
       </c>
-      <c r="D19" s="14">
-        <v>15</v>
-      </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H19" s="15">
-        <v>-35.714285714285</v>
+        <v>-43.103448275862</v>
       </c>
       <c r="I19" s="14">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J19" s="14">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="K19" s="15">
-        <v>-14.705882352941</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.321428571428</v>
+        <v>-21.487603305785</v>
       </c>
       <c r="M19" s="15">
-        <v>-16.346153846153</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="N19" s="15">
-        <v>-32.558139534883</v>
+        <v>-33.566433566433</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
         <v>3</v>
@@ -1107,104 +1107,104 @@
         <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-12.5</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" s="15">
-        <v>13.793103448275</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>13.793103448275</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="M20" s="15">
-        <v>-43.103448275862</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.216981132075</v>
+        <v>-92.122538293216</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.571428571428</v>
+        <v>-40</v>
       </c>
       <c r="F21" s="17">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G21" s="17">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.848484848484</v>
+        <v>-24.358974358974</v>
       </c>
       <c r="I21" s="17">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="J21" s="17">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.921787709497</v>
+        <v>-17.587939698492</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.422680412371</v>
+        <v>-24.249422632794</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.017902813299</v>
+        <v>-23.543123543123</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.476923076923</v>
+        <v>-81.552305961754</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-100</v>
       </c>
       <c r="L22" s="15">
         <v>-100</v>
@@ -1213,7 +1213,7 @@
         <v>-100</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1251,10 +1251,10 @@
         <v>-100</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>23.076923076923</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
         <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>16</v>
+        <v>6.097560975609</v>
       </c>
       <c r="I24" s="14">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="J24" s="14">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="K24" s="15">
-        <v>21.505376344086</v>
+        <v>18.396226415094</v>
       </c>
       <c r="L24" s="15">
-        <v>3.196347031963</v>
+        <v>4.149377593361</v>
       </c>
       <c r="M24" s="15">
-        <v>25.555555555555</v>
+        <v>29.381443298969</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>27.272727272727</v>
+        <v>100</v>
       </c>
       <c r="I25" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J25" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K25" s="15">
-        <v>40.625</v>
+        <v>54.545454545454</v>
       </c>
       <c r="L25" s="15">
-        <v>40.625</v>
+        <v>30.769230769230</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>-36.363636363636</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G26" s="14">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.354838709677</v>
+        <v>-20</v>
       </c>
       <c r="I26" s="14">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="J26" s="14">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.109489051094</v>
+        <v>-7.643312101910</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.731707317073</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.75</v>
+        <v>-15.204678362573</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-45.454545454545</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>6</v>
       </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
         <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.111111111111</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1473,13 +1473,13 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
         <v>0</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.592592592592</v>
+        <v>-93.103448275862</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1514,13 +1514,13 @@
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         <v>100</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.307692307692</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L31" s="15">
         <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>91</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>2158</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>975</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>2607</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>699</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>2418</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>9002</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -879,7 +879,7 @@
         <v>-60</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
         <v>-60</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>3</v>
@@ -902,282 +902,282 @@
         <v>200</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-36.363636363636</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>40</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-61.111111111111</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-54.545454545454</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H16" s="15">
-        <v>-27.272727272727</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K16" s="15">
-        <v>-36.363636363636</v>
+        <v>-38.356164383561</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.243243243243</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.808988764044</v>
+        <v>-53.125</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.193308550185</v>
+        <v>-92.268041237113</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>-53.846153846153</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G17" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>2.040816326530</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="J17" s="14">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.882352941176</v>
+        <v>-9.803921568627</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.925170068027</v>
+        <v>-15.337423312883</v>
       </c>
       <c r="M17" s="15">
-        <v>75.342465753424</v>
+        <v>66.265060240963</v>
       </c>
       <c r="N17" s="15">
-        <v>-36</v>
+        <v>-38.116591928251</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="14">
         <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-71.428571428571</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-53.658536585365</v>
       </c>
       <c r="L18" s="15">
-        <v>-60.869565217391</v>
+        <v>-61.224489795918</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.571428571428</v>
+        <v>-79.347826086956</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.652173913043</v>
+        <v>-95.777777777777</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G19" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H19" s="15">
-        <v>-43.103448275862</v>
+        <v>-31.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J19" s="14">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.666666666666</v>
+        <v>-17.692307692307</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.487603305785</v>
+        <v>-18.939393939393</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.636363636363</v>
+        <v>-14.4</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.566433566433</v>
+        <v>-30.967741935483</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
+        <v>11</v>
+      </c>
+      <c r="G20" s="14">
         <v>10</v>
       </c>
-      <c r="G20" s="14">
-        <v>7</v>
-      </c>
       <c r="H20" s="15">
-        <v>42.857142857142</v>
+        <v>10</v>
       </c>
       <c r="I20" s="14">
+        <v>38</v>
+      </c>
+      <c r="J20" s="14">
         <v>36</v>
       </c>
-      <c r="J20" s="14">
-        <v>30</v>
-      </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L20" s="15">
-        <v>-2.702702702702</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.857142857142</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.122538293216</v>
+        <v>-92.132505175983</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-40</v>
+        <v>-36.538461538461</v>
       </c>
       <c r="F21" s="17">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G21" s="17">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.358974358974</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I21" s="17">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="J21" s="17">
-        <v>398</v>
+        <v>450</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.587939698492</v>
+        <v>-20.222222222222</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.249422632794</v>
+        <v>-24.579831932773</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.543123543123</v>
+        <v>-24.421052631578</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.552305961754</v>
+        <v>-81.311816762103</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,7 +1201,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="15">
         <v>-100</v>
@@ -1213,7 +1213,7 @@
         <v>-100</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1251,10 +1251,10 @@
         <v>-100</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>183.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H24" s="15">
-        <v>6.097560975609</v>
+        <v>40</v>
       </c>
       <c r="I24" s="14">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="J24" s="14">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="K24" s="15">
-        <v>18.396226415094</v>
+        <v>27.678571428571</v>
       </c>
       <c r="L24" s="15">
-        <v>4.149377593361</v>
+        <v>2.142857142857</v>
       </c>
       <c r="M24" s="15">
-        <v>29.381443298969</v>
+        <v>36.842105263157</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
         <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I25" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J25" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K25" s="15">
-        <v>54.545454545454</v>
+        <v>54.285714285714</v>
       </c>
       <c r="L25" s="15">
-        <v>30.769230769230</v>
+        <v>20</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>-20</v>
+        <v>42.105263157894</v>
       </c>
       <c r="F26" s="14">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G26" s="14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H26" s="15">
-        <v>-20</v>
+        <v>-13.75</v>
       </c>
       <c r="I26" s="14">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="J26" s="14">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.643312101910</v>
+        <v>-2.840909090909</v>
       </c>
       <c r="L26" s="15">
-        <v>-21.621621621621</v>
+        <v>-16.990291262135</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.204678362573</v>
+        <v>-8.064516129032</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1394,31 +1394,31 @@
         <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-25</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L27" s="15">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1428,38 +1428,38 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>29</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="I28" s="14">
         <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.555555555555</v>
+        <v>-15</v>
       </c>
       <c r="L28" s="15">
         <v>21.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1473,16 +1473,16 @@
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1494,13 +1494,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
         <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.103448275862</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1514,16 +1514,16 @@
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1535,54 +1535,54 @@
         <v>-60</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
         <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>91</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>2158</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>975</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>2607</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>699</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>2418</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>9002</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -879,7 +879,7 @@
         <v>-60</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M14" s="15">
         <v>-60</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>7</v>
+      </c>
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>200</v>
-      </c>
-      <c r="F15" s="14">
-        <v>8</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
@@ -920,13 +920,13 @@
         <v>-16.666666666666</v>
       </c>
       <c r="L15" s="15">
+        <v>25</v>
+      </c>
+      <c r="M15" s="15">
         <v>42.857142857142</v>
       </c>
-      <c r="M15" s="15">
-        <v>66.666666666666</v>
-      </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-52.380952380952</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.142857142857</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
         <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>-41.666666666666</v>
+        <v>-44</v>
       </c>
       <c r="I16" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J16" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K16" s="15">
-        <v>-38.356164383561</v>
+        <v>-37.662337662337</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.307692307692</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.125</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.268041237113</v>
+        <v>-92.270531400966</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>14</v>
+      </c>
+      <c r="D17" s="14">
         <v>10</v>
       </c>
-      <c r="D17" s="14">
-        <v>17</v>
-      </c>
       <c r="E17" s="15">
-        <v>-41.176470588235</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G17" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.222222222222</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="I17" s="14">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="J17" s="14">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.803921568627</v>
+        <v>-4.907975460122</v>
       </c>
       <c r="L17" s="15">
-        <v>-15.337423312883</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M17" s="15">
-        <v>66.265060240963</v>
+        <v>76.136363636363</v>
       </c>
       <c r="N17" s="15">
-        <v>-38.116591928251</v>
+        <v>-39.688715953307</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-80</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-76.470588235294</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="14">
         <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.658536585365</v>
+        <v>-51.219512195122</v>
       </c>
       <c r="L18" s="15">
-        <v>-61.224489795918</v>
+        <v>-59.183673469387</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.347826086956</v>
+        <v>-79.381443298969</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.777777777777</v>
+        <v>-95.841995841995</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G19" s="14">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.666666666666</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="I19" s="14">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J19" s="14">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.692307692307</v>
+        <v>-22.068965517241</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.939393939393</v>
+        <v>-19.858156028368</v>
       </c>
       <c r="M19" s="15">
-        <v>-14.4</v>
+        <v>-13.076923076923</v>
       </c>
       <c r="N19" s="15">
-        <v>-30.967741935483</v>
+        <v>-36.158192090395</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,10 +1101,10 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
         <v>11</v>
@@ -1116,22 +1116,22 @@
         <v>10</v>
       </c>
       <c r="I20" s="14">
+        <v>41</v>
+      </c>
+      <c r="J20" s="14">
         <v>38</v>
       </c>
-      <c r="J20" s="14">
-        <v>36</v>
-      </c>
       <c r="K20" s="15">
-        <v>5.555555555555</v>
+        <v>7.894736842105</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.627906976744</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="M20" s="15">
-        <v>-44.117647058823</v>
+        <v>-42.253521126760</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.132505175983</v>
+        <v>-91.929133858267</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.538461538461</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="F21" s="17">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G21" s="17">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.411764705882</v>
+        <v>-27.215189873417</v>
       </c>
       <c r="I21" s="17">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="J21" s="17">
-        <v>450</v>
+        <v>481</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.222222222222</v>
+        <v>-19.126819126819</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.579831932773</v>
+        <v>-22.970297029703</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.421052631578</v>
+        <v>-23.122529644268</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.311816762103</v>
+        <v>-81.234925229136</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14">
-        <v>3</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>183.333333333333</v>
+        <v>119.047619047619</v>
       </c>
       <c r="F24" s="14">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="G24" s="14">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H24" s="15">
-        <v>40</v>
+        <v>69.444444444444</v>
       </c>
       <c r="I24" s="14">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="J24" s="14">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="K24" s="15">
-        <v>27.678571428571</v>
+        <v>35.510204081632</v>
       </c>
       <c r="L24" s="15">
-        <v>2.142857142857</v>
+        <v>4.075235109717</v>
       </c>
       <c r="M24" s="15">
-        <v>36.842105263157</v>
+        <v>44.347826086956</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>60</v>
+        <v>266.666666666667</v>
       </c>
       <c r="I25" s="14">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J25" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" s="15">
-        <v>54.285714285714</v>
+        <v>72.222222222222</v>
       </c>
       <c r="L25" s="15">
-        <v>20</v>
+        <v>12.727272727272</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>27</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>42.105263157894</v>
+        <v>35</v>
       </c>
       <c r="F26" s="14">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G26" s="14">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.75</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="J26" s="14">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.840909090909</v>
+        <v>-0.510204081632</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.990291262135</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.064516129032</v>
+        <v>-3.465346534653</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>7</v>
+      </c>
+      <c r="G27" s="14">
         <v>3</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>200</v>
-      </c>
-      <c r="F27" s="14">
-        <v>8</v>
-      </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
@@ -1412,7 +1412,7 @@
         <v>-7.692307692307</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-62.5</v>
+        <v>-37.5</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-15</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L28" s="15">
-        <v>21.428571428571</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.818181818181</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.117647058823</v>
+        <v>-95.121951219512</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,46 +1510,46 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-77.777777777777</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.75</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -885,48 +885,48 @@
         <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>133.333333333333</v>
+        <v>60</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>-16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>42.857142857142</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N15" s="15">
-        <v>-52.380952380952</v>
+        <v>-47.826086956521</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
         <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J16" s="14">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.662337662337</v>
+        <v>-35</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.463414634146</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="M16" s="15">
-        <v>-55.555555555555</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.270531400966</v>
+        <v>-92.09726443769</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.094339622641</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="I17" s="14">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J17" s="14">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.907975460122</v>
+        <v>-12.154696132596</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.428571428571</v>
+        <v>-17.1875</v>
       </c>
       <c r="M17" s="15">
-        <v>76.136363636363</v>
+        <v>63.917525773195</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.688715953307</v>
+        <v>-42.805755395683</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
         <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.219512195122</v>
+        <v>-41.860465116279</v>
       </c>
       <c r="L18" s="15">
-        <v>-59.183673469387</v>
+        <v>-51.923076923076</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.381443298969</v>
+        <v>-75.728155339805</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.841995841995</v>
+        <v>-95.155038759689</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>-60</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" s="14">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-37.931034482758</v>
+        <v>-43.076923076923</v>
       </c>
       <c r="I19" s="14">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="J19" s="14">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.068965517241</v>
+        <v>-24.550898203592</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.858156028368</v>
+        <v>-17.105263157894</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.076923076923</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.158192090395</v>
+        <v>-32.978723404255</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
+        <v>10</v>
+      </c>
+      <c r="G20" s="14">
         <v>11</v>
       </c>
-      <c r="G20" s="14">
-        <v>10</v>
-      </c>
       <c r="H20" s="15">
-        <v>10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I20" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J20" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K20" s="15">
-        <v>7.894736842105</v>
+        <v>5</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.888888888888</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.253521126760</v>
+        <v>-44</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.929133858267</v>
+        <v>-92.377495462794</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.903225806451</v>
+        <v>-48</v>
       </c>
       <c r="F21" s="17">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G21" s="17">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.215189873417</v>
+        <v>-34.682080924855</v>
       </c>
       <c r="I21" s="17">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="J21" s="17">
-        <v>481</v>
+        <v>531</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.126819126819</v>
+        <v>-21.280602636534</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.970297029703</v>
+        <v>-23.302752293578</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.122529644268</v>
+        <v>-23.722627737226</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.234925229136</v>
+        <v>-81.205035971223</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,13 +1262,13 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>119.047619047619</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F24" s="14">
         <v>122</v>
@@ -1280,19 +1280,19 @@
         <v>69.444444444444</v>
       </c>
       <c r="I24" s="14">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="J24" s="14">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="K24" s="15">
-        <v>35.510204081632</v>
+        <v>34.883720930232</v>
       </c>
       <c r="L24" s="15">
-        <v>4.075235109717</v>
+        <v>2.052785923753</v>
       </c>
       <c r="M24" s="15">
-        <v>44.347826086956</v>
+        <v>39.759036144578</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,13 +1303,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
         <v>22</v>
@@ -1321,16 +1321,16 @@
         <v>266.666666666667</v>
       </c>
       <c r="I25" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J25" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K25" s="15">
-        <v>72.222222222222</v>
+        <v>76.315789473684</v>
       </c>
       <c r="L25" s="15">
-        <v>12.727272727272</v>
+        <v>19.642857142857</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>35</v>
+        <v>15.789473684210</v>
       </c>
       <c r="F26" s="14">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G26" s="14">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>14.102564102564</v>
       </c>
       <c r="I26" s="14">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="J26" s="14">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.510204081632</v>
+        <v>0.930232558139</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.958904109589</v>
+        <v>-4.405286343612</v>
       </c>
       <c r="M26" s="15">
-        <v>-3.465346534653</v>
+        <v>2.358490566037</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>133.333333333333</v>
+        <v>80</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>-7.692307692307</v>
+        <v>-6.25</v>
       </c>
       <c r="L27" s="15">
-        <v>9.090909090909</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K28" s="15">
-        <v>-13.043478260869</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>11.111111111111</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.121951219512</v>
+        <v>-95.348837209302</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-81.818181818181</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.736842105263</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
       </c>
       <c r="L31" s="15">
         <v>-50</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>60</v>
+        <v>-20</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>-31.25</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M15" s="15">
-        <v>71.428571428571</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N15" s="15">
-        <v>-47.826086956521</v>
+        <v>-57.692307692307</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>4</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I16" s="14">
         <v>52</v>
       </c>
       <c r="J16" s="14">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K16" s="15">
-        <v>-35</v>
+        <v>-37.349397590361</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.534883720930</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.666666666666</v>
+        <v>-58.4</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.09726443769</v>
+        <v>-92.507204610951</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-83.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H17" s="15">
-        <v>-37.931034482758</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I17" s="14">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="J17" s="14">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="K17" s="15">
-        <v>-12.154696132596</v>
+        <v>-12.435233160621</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.1875</v>
+        <v>-16.336633663366</v>
       </c>
       <c r="M17" s="15">
-        <v>63.917525773195</v>
+        <v>57.943925233644</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.805755395683</v>
+        <v>-44.039735099337</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-12.5</v>
+        <v>-30</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.860465116279</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L18" s="15">
-        <v>-51.923076923076</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="15">
-        <v>-75.728155339805</v>
+        <v>-77.192982456140</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.155038759689</v>
+        <v>-95.272727272727</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-45.454545454545</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>-43.076923076923</v>
+        <v>-36.764705882352</v>
       </c>
       <c r="I19" s="14">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J19" s="14">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.550898203592</v>
+        <v>-24.175824175824</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.105263157894</v>
+        <v>-15.853658536585</v>
       </c>
       <c r="M19" s="15">
-        <v>-10.638297872340</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="N19" s="15">
-        <v>-32.978723404255</v>
+        <v>-31.343283582089</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
         <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-9.090909090909</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I20" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J20" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K20" s="15">
-        <v>5</v>
+        <v>9.756097560975</v>
       </c>
       <c r="L20" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="15">
-        <v>-44</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.377495462794</v>
+        <v>-92.487479131886</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>-48</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G21" s="17">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H21" s="18">
-        <v>-34.682080924855</v>
+        <v>-31.547619047619</v>
       </c>
       <c r="I21" s="17">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="J21" s="17">
-        <v>531</v>
+        <v>566</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.280602636534</v>
+        <v>-21.731448763250</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.302752293578</v>
+        <v>-24.013722126929</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.722627737226</v>
+        <v>-24.013722126929</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.205035971223</v>
+        <v>-81.402183039462</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>38.461538461538</v>
+        <v>-12</v>
       </c>
       <c r="F24" s="14">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G24" s="14">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H24" s="15">
-        <v>69.444444444444</v>
+        <v>66.197183098591</v>
       </c>
       <c r="I24" s="14">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="J24" s="14">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="K24" s="15">
-        <v>34.883720930232</v>
+        <v>30.742049469964</v>
       </c>
       <c r="L24" s="15">
-        <v>2.052785923753</v>
+        <v>1.648351648351</v>
       </c>
       <c r="M24" s="15">
-        <v>39.759036144578</v>
+        <v>39.622641509434</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H25" s="15">
-        <v>266.666666666667</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J25" s="14">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K25" s="15">
-        <v>76.315789473684</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L25" s="15">
-        <v>19.642857142857</v>
+        <v>22.807017543859</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>15.789473684210</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F26" s="14">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G26" s="14">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>14.102564102564</v>
+        <v>17.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="J26" s="14">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="K26" s="15">
-        <v>0.930232558139</v>
+        <v>-0.431034482758</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.405286343612</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="M26" s="15">
-        <v>2.358490566037</v>
+        <v>1.762114537444</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-6.25</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" s="14">
         <v>24</v>
       </c>
       <c r="K28" s="15">
-        <v>-4.166666666666</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>21.052631578947</v>
+        <v>31.578947368421</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>-71.428571428571</v>
       </c>
       <c r="L29" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
         <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.348837209302</v>
+        <v>-95.918367346938</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M30" s="15">
         <v>-81.818181818181</v>
       </c>
       <c r="N30" s="15">
-        <v>-95</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -879,7 +879,7 @@
         <v>-60</v>
       </c>
       <c r="L14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
         <v>-60</v>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
         <v>16</v>
       </c>
       <c r="K15" s="15">
-        <v>-31.25</v>
+        <v>-18.75</v>
       </c>
       <c r="L15" s="15">
-        <v>22.222222222222</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M15" s="15">
-        <v>57.142857142857</v>
+        <v>44.444444444444</v>
       </c>
       <c r="N15" s="15">
-        <v>-57.692307692307</v>
+        <v>-51.851851851851</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>20</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-41.176470588235</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J16" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.349397590361</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.857142857142</v>
+        <v>-39.583333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.4</v>
+        <v>-57.352941176470</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.507204610951</v>
+        <v>-92.172739541160</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
+        <v>-6.25</v>
+      </c>
+      <c r="F17" s="14">
+        <v>43</v>
+      </c>
+      <c r="G17" s="14">
+        <v>56</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-23.214285714285</v>
+      </c>
+      <c r="I17" s="14">
+        <v>185</v>
+      </c>
+      <c r="J17" s="14">
+        <v>209</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-11.483253588516</v>
+      </c>
+      <c r="L17" s="15">
         <v>-16.666666666666</v>
       </c>
-      <c r="F17" s="14">
-        <v>39</v>
-      </c>
-      <c r="G17" s="14">
-        <v>57</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-31.578947368421</v>
-      </c>
-      <c r="I17" s="14">
-        <v>169</v>
-      </c>
-      <c r="J17" s="14">
-        <v>193</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-12.435233160621</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-16.336633663366</v>
-      </c>
       <c r="M17" s="15">
-        <v>57.943925233644</v>
+        <v>56.779661016949</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.039735099337</v>
+        <v>-42.724458204334</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-30</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.478260869565</v>
+        <v>-40.816326530612</v>
       </c>
       <c r="L18" s="15">
-        <v>-50</v>
+        <v>-45.283018867924</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.192982456140</v>
+        <v>-76.8</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.272727272727</v>
+        <v>-95.134228187919</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H19" s="15">
-        <v>-36.764705882352</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="I19" s="14">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="J19" s="14">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.175824175824</v>
+        <v>-19.680851063829</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.853658536585</v>
+        <v>-14.204545454545</v>
       </c>
       <c r="M19" s="15">
-        <v>-6.122448979591</v>
+        <v>-3.205128205128</v>
       </c>
       <c r="N19" s="15">
-        <v>-31.343283582089</v>
+        <v>-28.773584905660</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F20" s="14">
+        <v>17</v>
+      </c>
+      <c r="G20" s="14">
         <v>12</v>
       </c>
-      <c r="G20" s="14">
-        <v>11</v>
-      </c>
       <c r="H20" s="15">
-        <v>9.090909090909</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J20" s="14">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K20" s="15">
-        <v>9.756097560975</v>
+        <v>10.416666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-25</v>
+        <v>-15.873015873015</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.307692307692</v>
+        <v>-39.080459770114</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.487479131886</v>
+        <v>-91.833590138674</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>-25.714285714285</v>
+        <v>13.513513513513</v>
       </c>
       <c r="F21" s="17">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="G21" s="17">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="H21" s="18">
-        <v>-31.547619047619</v>
+        <v>-16.993464052287</v>
       </c>
       <c r="I21" s="17">
-        <v>443</v>
+        <v>491</v>
       </c>
       <c r="J21" s="17">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.731448763250</v>
+        <v>-18.573797678275</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.013722126929</v>
+        <v>-21.690590111642</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.013722126929</v>
+        <v>-22.798742138364</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.402183039462</v>
+        <v>-80.805316653635</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-12</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="G24" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H24" s="15">
-        <v>66.197183098591</v>
+        <v>22.5</v>
       </c>
       <c r="I24" s="14">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="J24" s="14">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="K24" s="15">
-        <v>30.742049469964</v>
+        <v>26.315789473684</v>
       </c>
       <c r="L24" s="15">
-        <v>1.648351648351</v>
+        <v>0.261096605744</v>
       </c>
       <c r="M24" s="15">
-        <v>39.622641509434</v>
+        <v>35.211267605633</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
         <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>58.333333333333</v>
+        <v>46.153846153846</v>
       </c>
       <c r="I25" s="14">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J25" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K25" s="15">
-        <v>55.555555555555</v>
+        <v>52.083333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>22.807017543859</v>
+        <v>23.728813559322</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-17.647058823529</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H26" s="15">
-        <v>17.333333333333</v>
+        <v>9.859154929577</v>
       </c>
       <c r="I26" s="14">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="J26" s="14">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.431034482758</v>
+        <v>-0.809716599190</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.941176470588</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="M26" s="15">
-        <v>1.762114537444</v>
+        <v>0.823045267489</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
         <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-17.647058823529</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>8</v>
@@ -1444,16 +1444,16 @@
         <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>31.578947368421</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>3</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>-71.428571428571</v>
+        <v>-70</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M29" s="15">
-        <v>-84.615384615384</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.918367346938</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L30" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-81.818181818181</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.652173913043</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="D31" s="14">
         <v>1</v>
       </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="15">
         <v>-50</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -879,54 +879,54 @@
         <v>-60</v>
       </c>
       <c r="L14" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M14" s="15">
         <v>-60</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I15" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" s="15">
-        <v>-18.75</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L15" s="15">
-        <v>18.181818181818</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M15" s="15">
-        <v>44.444444444444</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-51.851851851851</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>-13.333333333333</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I16" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J16" s="14">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.090909090909</v>
+        <v>-35.416666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.583333333333</v>
+        <v>-38.613861386138</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.352941176470</v>
+        <v>-57.241379310344</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.172739541160</v>
+        <v>-92.041078305519</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>-6.25</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F17" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.214285714285</v>
+        <v>-41.269841269841</v>
       </c>
       <c r="I17" s="14">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J17" s="14">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.483253588516</v>
+        <v>-14.601769911504</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.666666666666</v>
+        <v>-17.872340425531</v>
       </c>
       <c r="M17" s="15">
-        <v>56.779661016949</v>
+        <v>53.174603174603</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.724458204334</v>
+        <v>-43.235294117647</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>12.5</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I18" s="14">
         <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K18" s="15">
-        <v>-40.816326530612</v>
+        <v>-46.296296296296</v>
       </c>
       <c r="L18" s="15">
-        <v>-45.283018867924</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="15">
-        <v>-76.8</v>
+        <v>-77.692307692307</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.134228187919</v>
+        <v>-95.389507154213</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-29.310344827586</v>
+        <v>-22.807017543859</v>
       </c>
       <c r="I19" s="14">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="J19" s="14">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.680851063829</v>
+        <v>-20.297029702970</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.204545454545</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="M19" s="15">
-        <v>-3.205128205128</v>
+        <v>-1.829268292682</v>
       </c>
       <c r="N19" s="15">
-        <v>-28.773584905660</v>
+        <v>-28.444444444444</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>14.285714285714</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
         <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>41.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I20" s="14">
+        <v>57</v>
+      </c>
+      <c r="J20" s="14">
         <v>53</v>
       </c>
-      <c r="J20" s="14">
-        <v>48</v>
-      </c>
       <c r="K20" s="15">
-        <v>10.416666666666</v>
+        <v>7.547169811320</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.873015873015</v>
+        <v>-10.9375</v>
       </c>
       <c r="M20" s="15">
-        <v>-39.080459770114</v>
+        <v>-39.361702127659</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.833590138674</v>
+        <v>-91.810344827586</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E21" s="18">
-        <v>13.513513513513</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G21" s="17">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.993464052287</v>
+        <v>-29.069767441860</v>
       </c>
       <c r="I21" s="17">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="J21" s="17">
-        <v>603</v>
+        <v>653</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.573797678275</v>
+        <v>-20.980091883614</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.690590111642</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.798742138364</v>
+        <v>-23.328380386329</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.805316653635</v>
+        <v>-80.938308090136</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>53.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G24" s="14">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H24" s="15">
-        <v>22.5</v>
+        <v>11.494252873563</v>
       </c>
       <c r="I24" s="14">
-        <v>384</v>
+        <v>427</v>
       </c>
       <c r="J24" s="14">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="K24" s="15">
-        <v>26.315789473684</v>
+        <v>28.614457831325</v>
       </c>
       <c r="L24" s="15">
-        <v>0.261096605744</v>
+        <v>4.914004914004</v>
       </c>
       <c r="M24" s="15">
-        <v>35.211267605633</v>
+        <v>40.924092409240</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F25" s="14">
         <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>46.153846153846</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I25" s="14">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="J25" s="14">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="K25" s="15">
-        <v>52.083333333333</v>
+        <v>42.105263157894</v>
       </c>
       <c r="L25" s="15">
-        <v>23.728813559322</v>
+        <v>30.645161290322</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>6.666666666666</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F26" s="14">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G26" s="14">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H26" s="15">
-        <v>9.859154929577</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I26" s="14">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="J26" s="14">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.809716599190</v>
+        <v>-3.396226415094</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.921568627450</v>
+        <v>-5.185185185185</v>
       </c>
       <c r="M26" s="15">
-        <v>0.823045267489</v>
+        <v>-1.538461538461</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>21.428571428571</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>80</v>
       </c>
       <c r="I28" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J28" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>3.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>8.333333333333</v>
+        <v>16</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>-70</v>
+        <v>-75</v>
       </c>
       <c r="L29" s="15">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
         <v>-76.923076923076</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="M30" s="15">
         <v>-72.727272727272</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.75</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,79 +854,79 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="M14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" s="15">
-        <v>-29.411764705882</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="N15" s="15">
-        <v>-55.555555555555</v>
+        <v>-58.620689655172</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>8</v>
-      </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-26.315789473684</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J16" s="14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.416666666666</v>
+        <v>-33</v>
       </c>
       <c r="L16" s="15">
-        <v>-38.613861386138</v>
+        <v>-35.576923076923</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.241379310344</v>
+        <v>-56.493506493506</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.041078305519</v>
+        <v>-91.898428053204</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-58.823529411764</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F17" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G17" s="14">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H17" s="15">
-        <v>-41.269841269841</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I17" s="14">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="J17" s="14">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.601769911504</v>
+        <v>-14.644351464435</v>
       </c>
       <c r="L17" s="15">
-        <v>-17.872340425531</v>
+        <v>-18.4</v>
       </c>
       <c r="M17" s="15">
-        <v>53.174603174603</v>
+        <v>48.905109489051</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.235294117647</v>
+        <v>-43.016759776536</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-46.153846153846</v>
+        <v>-65</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J18" s="14">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.296296296296</v>
+        <v>-49.206349206349</v>
       </c>
       <c r="L18" s="15">
-        <v>-50</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.692307692307</v>
+        <v>-76.642335766423</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.389507154213</v>
+        <v>-95.252225519287</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E19" s="15">
+        <v>-39.130434782608</v>
+      </c>
+      <c r="F19" s="14">
+        <v>45</v>
+      </c>
+      <c r="G19" s="14">
+        <v>58</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-22.413793103448</v>
+      </c>
+      <c r="I19" s="14">
+        <v>175</v>
+      </c>
+      <c r="J19" s="14">
+        <v>225</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-17.061611374407</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-0.568181818181</v>
+      </c>
+      <c r="N19" s="15">
         <v>-28.571428571428</v>
-      </c>
-      <c r="F19" s="14">
-        <v>44</v>
-      </c>
-      <c r="G19" s="14">
-        <v>57</v>
-      </c>
-      <c r="H19" s="15">
-        <v>-22.807017543859</v>
-      </c>
-      <c r="I19" s="14">
-        <v>161</v>
-      </c>
-      <c r="J19" s="14">
-        <v>202</v>
-      </c>
-      <c r="K19" s="15">
-        <v>-20.297029702970</v>
-      </c>
-      <c r="L19" s="15">
-        <v>-17.857142857142</v>
-      </c>
-      <c r="M19" s="15">
-        <v>-1.829268292682</v>
-      </c>
-      <c r="N19" s="15">
-        <v>-28.444444444444</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
         <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>13.333333333333</v>
+        <v>40</v>
       </c>
       <c r="I20" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K20" s="15">
-        <v>7.547169811320</v>
+        <v>14.545454545454</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.9375</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M20" s="15">
-        <v>-39.361702127659</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.810344827586</v>
+        <v>-91.486486486486</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="F21" s="17">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G21" s="17">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.069767441860</v>
+        <v>-23.563218390804</v>
       </c>
       <c r="I21" s="17">
-        <v>516</v>
+        <v>555</v>
       </c>
       <c r="J21" s="17">
-        <v>653</v>
+        <v>706</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.980091883614</v>
+        <v>-21.388101983002</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.214285714285</v>
+        <v>-22.809457579972</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.328380386329</v>
+        <v>-22.809457579972</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.938308090136</v>
+        <v>-80.762564991334</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="I22" s="14">
+        <v>1</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M22" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1251,10 +1251,10 @@
         <v>-100</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>53.571428571428</v>
+        <v>10</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G24" s="14">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H24" s="15">
-        <v>11.494252873563</v>
+        <v>7.446808510638</v>
       </c>
       <c r="I24" s="14">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="J24" s="14">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="K24" s="15">
-        <v>28.614457831325</v>
+        <v>27.556818181818</v>
       </c>
       <c r="L24" s="15">
-        <v>4.914004914004</v>
+        <v>3.218390804597</v>
       </c>
       <c r="M24" s="15">
-        <v>40.924092409240</v>
+        <v>41.640378548895</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-11.111111111111</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>-9.523809523809</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I25" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J25" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K25" s="15">
-        <v>42.105263157894</v>
+        <v>37.704918032786</v>
       </c>
       <c r="L25" s="15">
-        <v>30.645161290322</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>-27.777777777777</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F26" s="14">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G26" s="14">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.695652173913</v>
+        <v>-7.8125</v>
       </c>
       <c r="I26" s="14">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="J26" s="14">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.396226415094</v>
+        <v>-2.150537634408</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.185185185185</v>
+        <v>-5.536332179930</v>
       </c>
       <c r="M26" s="15">
-        <v>-1.538461538461</v>
+        <v>-0.364963503649</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1394,54 +1394,54 @@
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K27" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
         <v>29</v>
@@ -1453,13 +1453,13 @@
         <v>3.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>16</v>
+        <v>11.538461538461</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1479,28 +1479,28 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>-80</v>
+        <v>-87.5</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K29" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-70</v>
       </c>
       <c r="M29" s="15">
-        <v>-76.923076923076</v>
+        <v>-81.25</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.444444444444</v>
+        <v>-94.642857142857</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1511,7 +1511,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="15">
         <v>-100</v>
@@ -1520,28 +1520,28 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K30" s="15">
+        <v>-75</v>
+      </c>
+      <c r="L30" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L30" s="15">
-        <v>-62.5</v>
-      </c>
       <c r="M30" s="15">
-        <v>-72.727272727272</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.339622641509</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,13 +1555,13 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1579,10 +1579,10 @@
         <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>91</v>

--- a/data/source/weekly/cs-en-us-067pct.xlsx
+++ b/data/source/weekly/cs-en-us-067pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
@@ -899,16 +899,16 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>12</v>
@@ -926,7 +926,7 @@
         <v>20</v>
       </c>
       <c r="N15" s="15">
-        <v>-58.620689655172</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I16" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J16" s="14">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K16" s="15">
-        <v>-33</v>
+        <v>-31.132075471698</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.576923076923</v>
+        <v>-31.775700934579</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.493506493506</v>
+        <v>-53.797468354430</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.898428053204</v>
+        <v>-91.541135573580</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
         <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-23.076923076923</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F17" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G17" s="14">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H17" s="15">
-        <v>-24.137931034482</v>
+        <v>-22.033898305084</v>
       </c>
       <c r="I17" s="14">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="J17" s="14">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.644351464435</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>-18.4</v>
+        <v>-19.402985074626</v>
       </c>
       <c r="M17" s="15">
-        <v>48.905109489051</v>
+        <v>48.965517241379</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.016759776536</v>
+        <v>-43.307086614173</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
         <v>9</v>
       </c>
-      <c r="E18" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F18" s="14">
-        <v>7</v>
-      </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-65</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J18" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K18" s="15">
-        <v>-49.206349206349</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L18" s="15">
-        <v>-52.941176470588</v>
+        <v>-55.128205128205</v>
       </c>
       <c r="M18" s="15">
-        <v>-76.642335766423</v>
+        <v>-76.351351351351</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.252225519287</v>
+        <v>-95.063469675599</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-39.130434782608</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
         <v>58</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.413793103448</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I19" s="14">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="J19" s="14">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.222222222222</v>
+        <v>-21.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.061611374407</v>
+        <v>-14.155251141552</v>
       </c>
       <c r="M19" s="15">
-        <v>-0.568181818181</v>
+        <v>0</v>
       </c>
       <c r="N19" s="15">
-        <v>-28.571428571428</v>
+        <v>-27.413127413127</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>40</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I20" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J20" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K20" s="15">
-        <v>14.545454545454</v>
+        <v>8.064516129032</v>
       </c>
       <c r="L20" s="15">
-        <v>-4.545454545454</v>
+        <v>-4.285714285714</v>
       </c>
       <c r="M20" s="15">
-        <v>-36.363636363636</v>
+        <v>-35.576923076923</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.486486486486</v>
+        <v>-91.388174807197</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.923076923076</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="F21" s="17">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="G21" s="17">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.563218390804</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>555</v>
+        <v>593</v>
       </c>
       <c r="J21" s="17">
-        <v>706</v>
+        <v>749</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.388101983002</v>
+        <v>-20.827770360480</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.809457579972</v>
+        <v>-22.178477690288</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.809457579972</v>
+        <v>-21.870882740448</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.762564991334</v>
+        <v>-80.441952506596</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1227,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1236,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1251,10 +1251,10 @@
         <v>-100</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>29</v>
+      </c>
+      <c r="D24" s="14">
         <v>22</v>
       </c>
-      <c r="D24" s="14">
-        <v>20</v>
-      </c>
       <c r="E24" s="15">
-        <v>10</v>
+        <v>31.818181818181</v>
       </c>
       <c r="F24" s="14">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G24" s="14">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>7.446808510638</v>
+        <v>18.681318681318</v>
       </c>
       <c r="I24" s="14">
-        <v>449</v>
+        <v>478</v>
       </c>
       <c r="J24" s="14">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="K24" s="15">
-        <v>27.556818181818</v>
+        <v>27.807486631016</v>
       </c>
       <c r="L24" s="15">
-        <v>3.218390804597</v>
+        <v>3.913043478260</v>
       </c>
       <c r="M24" s="15">
-        <v>41.640378548895</v>
+        <v>42.261904761904</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-26.086956521739</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I25" s="14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J25" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K25" s="15">
-        <v>37.704918032786</v>
+        <v>31.343283582089</v>
       </c>
       <c r="L25" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>18</v>
+      </c>
+      <c r="D26" s="14">
         <v>17</v>
       </c>
-      <c r="D26" s="14">
-        <v>14</v>
-      </c>
       <c r="E26" s="15">
-        <v>21.428571428571</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F26" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G26" s="14">
         <v>64</v>
       </c>
       <c r="H26" s="15">
-        <v>-7.8125</v>
+        <v>-4.6875</v>
       </c>
       <c r="I26" s="14">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="J26" s="14">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.150537634408</v>
+        <v>-2.364864864864</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.536332179930</v>
+        <v>-8.544303797468</v>
       </c>
       <c r="M26" s="15">
-        <v>-0.364963503649</v>
+        <v>-1.700680272108</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>16</v>
@@ -1412,54 +1412,54 @@
         <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
+        <v>31</v>
+      </c>
+      <c r="J28" s="14">
         <v>29</v>
       </c>
-      <c r="J28" s="14">
-        <v>28</v>
-      </c>
       <c r="K28" s="15">
-        <v>3.571428571428</v>
+        <v>6.896551724137</v>
       </c>
       <c r="L28" s="15">
-        <v>11.538461538461</v>
+        <v>14.814814814814</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>3</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
@@ -1497,10 +1497,10 @@
         <v>-70</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.25</v>
+        <v>-82.352941176470</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.642857142857</v>
+        <v>-94.915254237288</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>3</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1538,10 +1538,10 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-78.571428571428</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.339622641509</v>
+        <v>-94.642857142857</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,13 +1576,13 @@
         <v>-50</v>
       </c>
       <c r="L31" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>91</v>
